--- a/py project/rocket/generated_data/initial_sets/rocket_initial_n50.xlsx
+++ b/py project/rocket/generated_data/initial_sets/rocket_initial_n50.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>头锥外形参数</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
@@ -499,35 +504,38 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>15.5</v>
+        <v>16.37387882212125</v>
       </c>
       <c r="I2" t="n">
-        <v>3.13</v>
+        <v>2.67098310047277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.96</v>
+        <v>0.825966223560864</v>
       </c>
       <c r="K2" t="n">
-        <v>48.8</v>
+        <v>40.44451988740299</v>
       </c>
       <c r="L2" t="n">
-        <v>1.89</v>
+        <v>1.362145866322217</v>
       </c>
       <c r="M2" t="n">
-        <v>26.7</v>
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>57.5726665491</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +554,38 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12.9</v>
+        <v>19.52965541942508</v>
       </c>
       <c r="I3" t="n">
-        <v>2.81</v>
+        <v>2.558878058677729</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5522022372862954</v>
       </c>
       <c r="K3" t="n">
-        <v>41.3</v>
+        <v>34.63818000021116</v>
       </c>
       <c r="L3" t="n">
-        <v>1.96</v>
+        <v>1.199774744493314</v>
       </c>
       <c r="M3" t="n">
-        <v>130</v>
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>76.85219944409999</v>
       </c>
     </row>
     <row r="4">
@@ -593,35 +604,38 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.3</v>
+        <v>12.05784724697285</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>2.220712161825687</v>
       </c>
       <c r="J4" t="n">
-        <v>0.63</v>
+        <v>0.4477884924212007</v>
       </c>
       <c r="K4" t="n">
-        <v>37.4</v>
+        <v>45.31644005178394</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.548853023514769</v>
       </c>
       <c r="M4" t="n">
-        <v>227</v>
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>167.9411275797</v>
       </c>
     </row>
     <row r="5">
@@ -640,35 +654,38 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>4.446980438499887</v>
       </c>
       <c r="I5" t="n">
-        <v>3.97</v>
+        <v>3.417951878806509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1</v>
+        <v>0.6822199278186009</v>
       </c>
       <c r="K5" t="n">
-        <v>45.6</v>
+        <v>31.69959520703046</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.600511198896745</v>
       </c>
       <c r="M5" t="n">
-        <v>7.59</v>
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>51.760250046</v>
       </c>
     </row>
     <row r="6">
@@ -687,35 +704,38 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>12.72181122202875</v>
       </c>
       <c r="I6" t="n">
-        <v>4.17</v>
+        <v>2.327277612032224</v>
       </c>
       <c r="J6" t="n">
-        <v>0.13</v>
+        <v>0.3601606783612988</v>
       </c>
       <c r="K6" t="n">
-        <v>33.9</v>
+        <v>32.06810480911675</v>
       </c>
       <c r="L6" t="n">
-        <v>1.86</v>
+        <v>1.685308219993313</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>214.6873479375</v>
       </c>
     </row>
     <row r="7">
@@ -734,35 +754,38 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18.7</v>
+        <v>8.209597497121898</v>
       </c>
       <c r="I7" t="n">
-        <v>4.81</v>
+        <v>4.317790679156431</v>
       </c>
       <c r="J7" t="n">
-        <v>0.86</v>
+        <v>0.9645553175533036</v>
       </c>
       <c r="K7" t="n">
-        <v>36.7</v>
+        <v>35.9989658735982</v>
       </c>
       <c r="L7" t="n">
-        <v>1.18</v>
+        <v>1.099791601453086</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5.9373108828</v>
       </c>
     </row>
     <row r="8">
@@ -781,35 +804,38 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17.9</v>
+        <v>19.66092770542951</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.120813381380549</v>
       </c>
       <c r="J8" t="n">
-        <v>0.65</v>
+        <v>0.8816953038135477</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>46.83161935550634</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.076566216321727</v>
       </c>
       <c r="M8" t="n">
-        <v>4.59</v>
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14.5250194773</v>
       </c>
     </row>
     <row r="9">
@@ -828,35 +854,38 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>13.35851340643694</v>
       </c>
       <c r="I9" t="n">
-        <v>2.39</v>
+        <v>3.316963759980339</v>
       </c>
       <c r="J9" t="n">
-        <v>0.83</v>
+        <v>0.5211474383233654</v>
       </c>
       <c r="K9" t="n">
-        <v>45.5</v>
+        <v>49.65052850056564</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.117765356558657</v>
       </c>
       <c r="M9" t="n">
-        <v>146</v>
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.9576512539</v>
       </c>
     </row>
     <row r="10">
@@ -875,35 +904,38 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>11.70356167132605</v>
       </c>
       <c r="I10" t="n">
-        <v>4.69</v>
+        <v>3.505688030750509</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67</v>
+        <v>0.1766453390078895</v>
       </c>
       <c r="K10" t="n">
-        <v>32.9</v>
+        <v>39.93892890947732</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15</v>
+        <v>1.865526514716878</v>
       </c>
       <c r="M10" t="n">
-        <v>5.65</v>
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34.1023893838</v>
       </c>
     </row>
     <row r="11">
@@ -922,35 +954,38 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11.1</v>
+        <v>13.78516105889416</v>
       </c>
       <c r="I11" t="n">
-        <v>4.97</v>
+        <v>2.109311310862322</v>
       </c>
       <c r="J11" t="n">
-        <v>0.14</v>
+        <v>0.02842806973553856</v>
       </c>
       <c r="K11" t="n">
-        <v>44.2</v>
+        <v>46.54195641722049</v>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>1.308377229256641</v>
       </c>
       <c r="M11" t="n">
-        <v>0.64</v>
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>192.6513325381</v>
       </c>
     </row>
     <row r="12">
@@ -969,35 +1004,38 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>18.78373752913801</v>
       </c>
       <c r="I12" t="n">
-        <v>3.99</v>
+        <v>3.740121042783432</v>
       </c>
       <c r="J12" t="n">
-        <v>0.82</v>
+        <v>0.9941932878435711</v>
       </c>
       <c r="K12" t="n">
-        <v>40.6</v>
+        <v>43.15597550605903</v>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>1.639391650323544</v>
       </c>
       <c r="M12" t="n">
-        <v>7.19</v>
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.8343902754</v>
       </c>
     </row>
     <row r="13">
@@ -1016,35 +1054,38 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>17.90960477329926</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>2.838764950478345</v>
       </c>
       <c r="J13" t="n">
-        <v>0.24</v>
+        <v>0.3840037301417803</v>
       </c>
       <c r="K13" t="n">
-        <v>42.6</v>
+        <v>37.90784345966468</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.474462368221752</v>
       </c>
       <c r="M13" t="n">
-        <v>6.25</v>
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>61.3341641094</v>
       </c>
     </row>
     <row r="14">
@@ -1063,35 +1104,38 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.3</v>
+        <v>6.320343031684029</v>
       </c>
       <c r="I14" t="n">
-        <v>4.63</v>
+        <v>3.206655056717092</v>
       </c>
       <c r="J14" t="n">
-        <v>0.91</v>
+        <v>0.09970098867989506</v>
       </c>
       <c r="K14" t="n">
-        <v>43.3</v>
+        <v>32.8912750999494</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>1.754608590218441</v>
       </c>
       <c r="M14" t="n">
-        <v>0.27</v>
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>80.691107264</v>
       </c>
     </row>
     <row r="15">
@@ -1110,35 +1154,38 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11.2</v>
+        <v>10.89563934026995</v>
       </c>
       <c r="I15" t="n">
-        <v>3.71</v>
+        <v>4.470448889923732</v>
       </c>
       <c r="J15" t="n">
-        <v>0.32</v>
+        <v>0.185601530964792</v>
       </c>
       <c r="K15" t="n">
-        <v>33.5</v>
+        <v>36.7283880435686</v>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>1.662316292094468</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.0610482924</v>
       </c>
     </row>
     <row r="16">
@@ -1157,35 +1204,38 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>16.59079974769701</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>2.25778937525144</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.7711412479801395</v>
       </c>
       <c r="K16" t="n">
-        <v>35.8</v>
+        <v>36.17998247017236</v>
       </c>
       <c r="L16" t="n">
-        <v>1.69</v>
+        <v>1.208417213933543</v>
       </c>
       <c r="M16" t="n">
-        <v>24.6</v>
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>121.2120844014</v>
       </c>
     </row>
     <row r="17">
@@ -1204,35 +1254,38 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>15.6</v>
+        <v>10.24408169109964</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>4.573941309223276</v>
       </c>
       <c r="J17" t="n">
-        <v>0.23</v>
+        <v>0.6462323898884751</v>
       </c>
       <c r="K17" t="n">
-        <v>47.4</v>
+        <v>30.76292234627978</v>
       </c>
       <c r="L17" t="n">
-        <v>1.26</v>
+        <v>1.817025226503707</v>
       </c>
       <c r="M17" t="n">
-        <v>77.59999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.7574262376</v>
       </c>
     </row>
     <row r="18">
@@ -1251,35 +1304,38 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.5</v>
+        <v>2.181473024086785</v>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>4.696132473059746</v>
       </c>
       <c r="J18" t="n">
-        <v>0.44</v>
+        <v>0.72556555877586</v>
       </c>
       <c r="K18" t="n">
-        <v>31.5</v>
+        <v>42.68037741071125</v>
       </c>
       <c r="L18" t="n">
-        <v>1.57</v>
+        <v>1.326369343961168</v>
       </c>
       <c r="M18" t="n">
-        <v>73.3</v>
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.1496849614</v>
       </c>
     </row>
     <row r="19">
@@ -1298,35 +1354,38 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.304405039684532</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>2.734296094352104</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.6783170971436624</v>
       </c>
       <c r="K19" t="n">
-        <v>44.6</v>
+        <v>30.09368441103652</v>
       </c>
       <c r="L19" t="n">
-        <v>1.81</v>
+        <v>1.57378826521378</v>
       </c>
       <c r="M19" t="n">
-        <v>25.9</v>
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>131.0755394017</v>
       </c>
     </row>
     <row r="20">
@@ -1345,35 +1404,38 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>16.97637969868612</v>
       </c>
       <c r="I20" t="n">
-        <v>2.26</v>
+        <v>3.188308140982806</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.5837586411853678</v>
       </c>
       <c r="K20" t="n">
-        <v>49.5</v>
+        <v>33.79015195523675</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.382881159234448</v>
       </c>
       <c r="M20" t="n">
-        <v>159</v>
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>34.4150154681</v>
       </c>
     </row>
     <row r="21">
@@ -1392,35 +1454,38 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>8.492372780092968</v>
       </c>
       <c r="I21" t="n">
-        <v>4.13</v>
+        <v>3.052336694469099</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.1581190704766841</v>
       </c>
       <c r="K21" t="n">
-        <v>36.1</v>
+        <v>38.15078041051912</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.299657099753967</v>
       </c>
       <c r="M21" t="n">
-        <v>11.8</v>
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>55.0152354278</v>
       </c>
     </row>
     <row r="22">
@@ -1439,35 +1504,38 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>2.850169178632843</v>
       </c>
       <c r="I22" t="n">
-        <v>3.55</v>
+        <v>3.610528197364803</v>
       </c>
       <c r="J22" t="n">
-        <v>0.84</v>
+        <v>0.9096451070034045</v>
       </c>
       <c r="K22" t="n">
-        <v>42</v>
+        <v>43.69560751434514</v>
       </c>
       <c r="L22" t="n">
-        <v>1.74</v>
+        <v>1.986906358437934</v>
       </c>
       <c r="M22" t="n">
-        <v>17.3</v>
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>27.2494566456</v>
       </c>
     </row>
     <row r="23">
@@ -1486,35 +1554,38 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.6</v>
+        <v>1.060285464240022</v>
       </c>
       <c r="I23" t="n">
-        <v>3.58</v>
+        <v>4.052552096562903</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.8714534864869533</v>
       </c>
       <c r="K23" t="n">
-        <v>37.9</v>
+        <v>45.88353300661232</v>
       </c>
       <c r="L23" t="n">
-        <v>1.06</v>
+        <v>1.954521540451743</v>
       </c>
       <c r="M23" t="n">
-        <v>19.4</v>
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10.8524569171</v>
       </c>
     </row>
     <row r="24">
@@ -1533,35 +1604,38 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.9</v>
+        <v>3.860354445913859</v>
       </c>
       <c r="I24" t="n">
-        <v>2.01</v>
+        <v>4.990935275846489</v>
       </c>
       <c r="J24" t="n">
-        <v>0.76</v>
+        <v>0.423303050913898</v>
       </c>
       <c r="K24" t="n">
-        <v>47.8</v>
+        <v>41.32903677905455</v>
       </c>
       <c r="L24" t="n">
-        <v>1.74</v>
+        <v>1.158015660860802</v>
       </c>
       <c r="M24" t="n">
-        <v>306</v>
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.4747917083</v>
       </c>
     </row>
     <row r="25">
@@ -1580,35 +1654,38 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.4</v>
+        <v>5.073718043406778</v>
       </c>
       <c r="I25" t="n">
-        <v>2.35</v>
+        <v>2.38414455747938</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1</v>
+        <v>0.2428120838486841</v>
       </c>
       <c r="K25" t="n">
-        <v>39.8</v>
+        <v>35.39389873390543</v>
       </c>
       <c r="L25" t="n">
-        <v>1.22</v>
+        <v>1.162905175411109</v>
       </c>
       <c r="M25" t="n">
-        <v>139</v>
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>154.1217340321</v>
       </c>
     </row>
     <row r="26">
@@ -1627,35 +1704,38 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>8.699999999999999</v>
+        <v>7.406363878893277</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>3.342969279052496</v>
       </c>
       <c r="J26" t="n">
-        <v>0.54</v>
+        <v>0.5778618322373683</v>
       </c>
       <c r="K26" t="n">
-        <v>40.2</v>
+        <v>39.11134130245397</v>
       </c>
       <c r="L26" t="n">
-        <v>1.03</v>
+        <v>1.969651018863086</v>
       </c>
       <c r="M26" t="n">
-        <v>147</v>
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>49.3929992073</v>
       </c>
     </row>
     <row r="27">
@@ -1674,35 +1754,38 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9.9</v>
+        <v>14.25374327822849</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>3.921149253583232</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02</v>
+        <v>0.462747990269701</v>
       </c>
       <c r="K27" t="n">
-        <v>38.4</v>
+        <v>31.59777268345691</v>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>1.500591409752095</v>
       </c>
       <c r="M27" t="n">
-        <v>262</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>17.1918576207</v>
       </c>
     </row>
     <row r="28">
@@ -1721,35 +1804,38 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>14.2</v>
+        <v>6.947074209869223</v>
       </c>
       <c r="I28" t="n">
-        <v>2.91</v>
+        <v>2.434810238425361</v>
       </c>
       <c r="J28" t="n">
-        <v>0.28</v>
+        <v>0.9343372416621826</v>
       </c>
       <c r="K28" t="n">
-        <v>38.6</v>
+        <v>34.14405749236745</v>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>1.77779171914786</v>
       </c>
       <c r="M28" t="n">
-        <v>87.5</v>
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>220.3629317908</v>
       </c>
     </row>
     <row r="29">
@@ -1768,35 +1854,38 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>16.6</v>
+        <v>17.30191640725176</v>
       </c>
       <c r="I29" t="n">
-        <v>2.71</v>
+        <v>4.360251621569196</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.4009648541646733</v>
       </c>
       <c r="K29" t="n">
-        <v>40.9</v>
+        <v>49.2318768047658</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.126281491808617</v>
       </c>
       <c r="M29" t="n">
-        <v>50.5</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.5364124969</v>
       </c>
     </row>
     <row r="30">
@@ -1815,35 +1904,38 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.2</v>
+        <v>9.152790436221739</v>
       </c>
       <c r="I30" t="n">
-        <v>3.32</v>
+        <v>4.765487429858103</v>
       </c>
       <c r="J30" t="n">
-        <v>0.44</v>
+        <v>0.305506662799958</v>
       </c>
       <c r="K30" t="n">
-        <v>30.8</v>
+        <v>47.35948093308301</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.492160430455838</v>
       </c>
       <c r="M30" t="n">
-        <v>33.6</v>
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.447535099</v>
       </c>
     </row>
     <row r="31">
@@ -1862,35 +1954,38 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>18.35272024987407</v>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>2.870325955641044</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.812819164691081</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>48.04177056256525</v>
       </c>
       <c r="L31" t="n">
-        <v>1.54</v>
+        <v>1.938378288431001</v>
       </c>
       <c r="M31" t="n">
-        <v>9.25</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>48.4734071633</v>
       </c>
     </row>
     <row r="32">
@@ -1909,35 +2004,38 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>12.5</v>
+        <v>0.06895429156365278</v>
       </c>
       <c r="I32" t="n">
-        <v>4.35</v>
+        <v>2.954317326424651</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3</v>
+        <v>0.04565175543915655</v>
       </c>
       <c r="K32" t="n">
-        <v>44.9</v>
+        <v>30.88857342438375</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1.24513949106559</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6</v>
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>82.77906495889999</v>
       </c>
     </row>
     <row r="33">
@@ -1956,35 +2054,38 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4.8</v>
+        <v>0.4950098723996657</v>
       </c>
       <c r="I33" t="n">
-        <v>3.65</v>
+        <v>4.427383238714963</v>
       </c>
       <c r="J33" t="n">
-        <v>0.62</v>
+        <v>0.7835026304708869</v>
       </c>
       <c r="K33" t="n">
-        <v>35.2</v>
+        <v>36.83970745513977</v>
       </c>
       <c r="L33" t="n">
-        <v>1.35</v>
+        <v>1.528638159685491</v>
       </c>
       <c r="M33" t="n">
-        <v>25.5</v>
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>7.9370944503</v>
       </c>
     </row>
     <row r="34">
@@ -2003,35 +2104,38 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3.9</v>
+        <v>14.60068454791946</v>
       </c>
       <c r="I34" t="n">
-        <v>3.07</v>
+        <v>3.672762375126667</v>
       </c>
       <c r="J34" t="n">
-        <v>0.38</v>
+        <v>0.3281548149273629</v>
       </c>
       <c r="K34" t="n">
-        <v>42.3</v>
+        <v>33.31207504330273</v>
       </c>
       <c r="L34" t="n">
-        <v>1.97</v>
+        <v>1.646455199949714</v>
       </c>
       <c r="M34" t="n">
-        <v>79.2</v>
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>26.5617329398</v>
       </c>
     </row>
     <row r="35">
@@ -2050,35 +2154,38 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.1</v>
+        <v>15.27597319159936</v>
       </c>
       <c r="I35" t="n">
-        <v>3.26</v>
+        <v>4.227537426761318</v>
       </c>
       <c r="J35" t="n">
-        <v>0.46</v>
+        <v>0.5162171888307795</v>
       </c>
       <c r="K35" t="n">
-        <v>35.5</v>
+        <v>47.89143947736042</v>
       </c>
       <c r="L35" t="n">
-        <v>1.83</v>
+        <v>1.400018918125391</v>
       </c>
       <c r="M35" t="n">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.2806265357</v>
       </c>
     </row>
     <row r="36">
@@ -2097,35 +2204,38 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>6.3</v>
+        <v>12.90458237688196</v>
       </c>
       <c r="I36" t="n">
-        <v>4.74</v>
+        <v>2.984446854269541</v>
       </c>
       <c r="J36" t="n">
-        <v>0.19</v>
+        <v>0.9511063339854541</v>
       </c>
       <c r="K36" t="n">
-        <v>39</v>
+        <v>35.12676930567594</v>
       </c>
       <c r="L36" t="n">
-        <v>1.77</v>
+        <v>1.00611751601745</v>
       </c>
       <c r="M36" t="n">
-        <v>1.03</v>
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>37.8052156942</v>
       </c>
     </row>
     <row r="37">
@@ -2144,35 +2254,38 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>13.9</v>
+        <v>10.55507069901197</v>
       </c>
       <c r="I37" t="n">
-        <v>4.05</v>
+        <v>2.514379952720379</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06</v>
+        <v>0.8476444822429394</v>
       </c>
       <c r="K37" t="n">
-        <v>30.7</v>
+        <v>43.46944808356175</v>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.782018609809871</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>126.2978510569</v>
       </c>
     </row>
     <row r="38">
@@ -2191,35 +2304,38 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>16.3</v>
+        <v>7.700880102862567</v>
       </c>
       <c r="I38" t="n">
-        <v>4.32</v>
+        <v>3.800505170938978</v>
       </c>
       <c r="J38" t="n">
-        <v>0.37</v>
+        <v>0.4960884827174407</v>
       </c>
       <c r="K38" t="n">
-        <v>34.3</v>
+        <v>48.72714297273237</v>
       </c>
       <c r="L38" t="n">
-        <v>1.11</v>
+        <v>1.851400725501327</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>11.8491181556</v>
       </c>
     </row>
     <row r="39">
@@ -2238,35 +2354,38 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3.5</v>
+        <v>6.421972705883081</v>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>2.045568100955467</v>
       </c>
       <c r="J39" t="n">
-        <v>0.21</v>
+        <v>0.6148491902040486</v>
       </c>
       <c r="K39" t="n">
-        <v>37.2</v>
+        <v>46.34818311111464</v>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>1.735156525417401</v>
       </c>
       <c r="M39" t="n">
-        <v>2.72</v>
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>298.8483748856</v>
       </c>
     </row>
     <row r="40">
@@ -2285,35 +2404,38 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.7</v>
+        <v>5.894421219916866</v>
       </c>
       <c r="I40" t="n">
-        <v>4.85</v>
+        <v>4.594506968238846</v>
       </c>
       <c r="J40" t="n">
-        <v>0.34</v>
+        <v>0.00381240182762413</v>
       </c>
       <c r="K40" t="n">
-        <v>42.9</v>
+        <v>42.21942024798888</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.421313197402994</v>
       </c>
       <c r="M40" t="n">
-        <v>0.793</v>
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.4554703463</v>
       </c>
     </row>
     <row r="41">
@@ -2332,35 +2454,38 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>19.4</v>
+        <v>14.8568706225234</v>
       </c>
       <c r="I41" t="n">
-        <v>2.74</v>
+        <v>2.174137589299679</v>
       </c>
       <c r="J41" t="n">
-        <v>0.92</v>
+        <v>0.7523397989385314</v>
       </c>
       <c r="K41" t="n">
-        <v>46.3</v>
+        <v>32.58232675814314</v>
       </c>
       <c r="L41" t="n">
-        <v>1.1</v>
+        <v>1.262268382756629</v>
       </c>
       <c r="M41" t="n">
-        <v>29.5</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>166.2848848034</v>
       </c>
     </row>
     <row r="42">
@@ -2379,35 +2504,38 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>9.9</v>
+        <v>15.88197415235287</v>
       </c>
       <c r="I42" t="n">
-        <v>2.61</v>
+        <v>4.036519811537346</v>
       </c>
       <c r="J42" t="n">
-        <v>0.52</v>
+        <v>0.7123179275858083</v>
       </c>
       <c r="K42" t="n">
-        <v>32.8</v>
+        <v>40.28230493446394</v>
       </c>
       <c r="L42" t="n">
-        <v>1.18</v>
+        <v>1.705588150482753</v>
       </c>
       <c r="M42" t="n">
-        <v>109</v>
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6.3424298301</v>
       </c>
     </row>
     <row r="43">
@@ -2426,35 +2554,38 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>9.300000000000001</v>
+        <v>1.303591116722199</v>
       </c>
       <c r="I43" t="n">
-        <v>4.54</v>
+        <v>3.917236916310854</v>
       </c>
       <c r="J43" t="n">
-        <v>0.28</v>
+        <v>0.2845642284007999</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>44.90119504411423</v>
       </c>
       <c r="L43" t="n">
-        <v>1.79</v>
+        <v>1.582616886889544</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>10.936349087</v>
       </c>
     </row>
     <row r="44">
@@ -2473,35 +2604,38 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>7.7</v>
+        <v>4.095725258573612</v>
       </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>4.150980476202172</v>
       </c>
       <c r="J44" t="n">
-        <v>0.77</v>
+        <v>0.2780243464023297</v>
       </c>
       <c r="K44" t="n">
-        <v>49.7</v>
+        <v>48.92587849920547</v>
       </c>
       <c r="L44" t="n">
-        <v>1.67</v>
+        <v>1.341449681650696</v>
       </c>
       <c r="M44" t="n">
-        <v>20.1</v>
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.4463817208</v>
       </c>
     </row>
     <row r="45">
@@ -2520,35 +2654,38 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>19.7</v>
+        <v>1.687665996775535</v>
       </c>
       <c r="I45" t="n">
-        <v>2.59</v>
+        <v>3.68064058419459</v>
       </c>
       <c r="J45" t="n">
-        <v>0.97</v>
+        <v>0.1094186178873393</v>
       </c>
       <c r="K45" t="n">
-        <v>39.5</v>
+        <v>41.69710342249521</v>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>1.444020304030718</v>
       </c>
       <c r="M45" t="n">
-        <v>59.8</v>
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>18.5983110686</v>
       </c>
     </row>
     <row r="46">
@@ -2567,35 +2704,38 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>4.8</v>
+        <v>11.41431480531591</v>
       </c>
       <c r="I46" t="n">
-        <v>2.47</v>
+        <v>4.930238783937234</v>
       </c>
       <c r="J46" t="n">
-        <v>0.16</v>
+        <v>0.07753565963726432</v>
       </c>
       <c r="K46" t="n">
-        <v>43.9</v>
+        <v>39.25694815944031</v>
       </c>
       <c r="L46" t="n">
-        <v>1.6</v>
+        <v>1.835534192299052</v>
       </c>
       <c r="M46" t="n">
-        <v>149</v>
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.7466728924</v>
       </c>
     </row>
     <row r="47">
@@ -2614,35 +2754,38 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>4.1</v>
+        <v>3.29477468789382</v>
       </c>
       <c r="I47" t="n">
-        <v>3.36</v>
+        <v>4.832755872710072</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6</v>
+        <v>0.6258445402030217</v>
       </c>
       <c r="K47" t="n">
-        <v>49</v>
+        <v>41.02050390227176</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.919324500250122</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.9606975739</v>
       </c>
     </row>
     <row r="48">
@@ -2661,35 +2804,38 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.9</v>
+        <v>18.91896565606055</v>
       </c>
       <c r="I48" t="n">
-        <v>3.87</v>
+        <v>4.203753160577348</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.3437088067746328</v>
       </c>
       <c r="K48" t="n">
-        <v>32.4</v>
+        <v>38.52039807459567</v>
       </c>
       <c r="L48" t="n">
-        <v>1.29</v>
+        <v>1.891886412049054</v>
       </c>
       <c r="M48" t="n">
-        <v>21.5</v>
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1.0499022994</v>
       </c>
     </row>
     <row r="49">
@@ -2708,35 +2854,38 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.2</v>
+        <v>5.204434052104685</v>
       </c>
       <c r="I49" t="n">
-        <v>4.45</v>
+        <v>2.643022466983734</v>
       </c>
       <c r="J49" t="n">
-        <v>0.71</v>
+        <v>0.2142044493655893</v>
       </c>
       <c r="K49" t="n">
-        <v>48.3</v>
+        <v>44.48412377432574</v>
       </c>
       <c r="L49" t="n">
-        <v>1.26</v>
+        <v>1.226407689220148</v>
       </c>
       <c r="M49" t="n">
-        <v>1.07</v>
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>78.6733138475</v>
       </c>
     </row>
     <row r="50">
@@ -2755,35 +2904,38 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>14.7</v>
+        <v>2.672250064127873</v>
       </c>
       <c r="I50" t="n">
-        <v>4.26</v>
+        <v>3.473107539390603</v>
       </c>
       <c r="J50" t="n">
-        <v>0.73</v>
+        <v>0.120610747364022</v>
       </c>
       <c r="K50" t="n">
-        <v>46.5</v>
+        <v>44.12732438182068</v>
       </c>
       <c r="L50" t="n">
-        <v>1.06</v>
+        <v>1.047913473723157</v>
       </c>
       <c r="M50" t="n">
-        <v>0.777</v>
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>18.4360533387</v>
       </c>
     </row>
     <row r="51">
@@ -2802,35 +2954,38 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>initial</t>
+          <t>initial_lhs</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>rocketdata2.xlsx</t>
+          <t>openrocket</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>12.3</v>
+        <v>9.943681689899048</v>
       </c>
       <c r="I51" t="n">
-        <v>2.87</v>
+        <v>4.700727430361999</v>
       </c>
       <c r="J51" t="n">
-        <v>0.41</v>
+        <v>0.2273165350759853</v>
       </c>
       <c r="K51" t="n">
-        <v>34.5</v>
+        <v>37.51766451879087</v>
       </c>
       <c r="L51" t="n">
-        <v>1.63</v>
+        <v>1.021852446261446</v>
       </c>
       <c r="M51" t="n">
-        <v>84.3</v>
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.2142188704</v>
       </c>
     </row>
   </sheetData>
